--- a/data/outputs/Portfolio_Monthly_Diff.xlsx
+++ b/data/outputs/Portfolio_Monthly_Diff.xlsx
@@ -598,17 +598,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Acies Investments Fund I, L.P.</t>
+          <t>Cerebras Systems Inc (1)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,40 +633,40 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17.1125</v>
+        <v>39.99998336</v>
       </c>
       <c r="K2" t="n">
-        <v>17.1125</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="M2" t="n">
-        <v>15.7263875</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="N2" t="n">
-        <v>15.7263875</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="P2" t="n">
-        <v>1.386112500000001</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.386112500000001</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>-7.105427357601002e-15</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -678,40 +678,40 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>12.683716</v>
+        <v>286.4823928099999</v>
       </c>
       <c r="W2" t="n">
-        <v>14.034903</v>
+        <v>265.62083464</v>
       </c>
       <c r="X2" t="n">
-        <v>1.351186999999999</v>
+        <v>-20.86155816999991</v>
       </c>
       <c r="Y2" t="n">
-        <v>-3.042671499999999</v>
+        <v>246.4824094499999</v>
       </c>
       <c r="Z2" t="n">
-        <v>-1.6914845</v>
+        <v>225.62085128</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.351186999999999</v>
+        <v>-20.86155816999988</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8065244481607744</v>
+        <v>7.162062799668123</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.8924429084556132</v>
+        <v>6.640523628457831</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.08591846029483885</v>
+        <v>-0.5215391712102928</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.05492458454080403</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.02935277732578557</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.02557180721501846</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -727,17 +727,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (1)</t>
+          <t>Cerebras Systems Inc (2)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -762,37 +762,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Capital SPV RSC Ltd</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Capital SPV RSC Ltd</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>39.99998336</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>39.99998336</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="M3" t="n">
-        <v>39.99998335999999</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>39.99998335999999</v>
+        <v>0.03513491000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>-6.938893903907228e-18</v>
       </c>
       <c r="P3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -807,41 +807,31 @@
         <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>318.618131</v>
+        <v>698.16579661</v>
       </c>
       <c r="W3" t="n">
-        <v>286.4823928099999</v>
+        <v>647.32558184</v>
       </c>
       <c r="X3" t="n">
-        <v>-32.1357381900001</v>
+        <v>-50.84021476999999</v>
       </c>
       <c r="Y3" t="n">
-        <v>278.61814764</v>
+        <v>698.1306617</v>
       </c>
       <c r="Z3" t="n">
-        <v>246.4824094499999</v>
+        <v>647.29044693</v>
       </c>
       <c r="AA3" t="n">
-        <v>-32.1357381900001</v>
+        <v>-50.84021476999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.965456588629942</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>7.162062799668123</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>-0.8033937889618183</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0.5552594721409149</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0.5091940466191891</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-0.04606542552172577</v>
-      </c>
+        <v>19871</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -856,17 +846,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (2)</t>
+          <t>MGX 1 Strategic Co-invest</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -891,82 +881,86 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.03513491000000001</v>
+        <v>296.60196</v>
       </c>
       <c r="K4" t="n">
-        <v>0.03513491000000001</v>
+        <v>296.60196</v>
       </c>
       <c r="L4" t="n">
-        <v>-6.938893903907228e-18</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03513491000000001</v>
+        <v>562.499557575</v>
       </c>
       <c r="N4" t="n">
-        <v>0.03513491000000001</v>
+        <v>294.251545</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.938893903907228e-18</v>
+        <v>-268.248012575</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-265.897597575</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.350415</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>268.248012575</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>249.9999988</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-249.9999988</v>
       </c>
       <c r="V4" t="n">
-        <v>776.481511</v>
+        <v>1180.373331</v>
       </c>
       <c r="W4" t="n">
-        <v>698.16579661</v>
+        <v>1180.373331</v>
       </c>
       <c r="X4" t="n">
-        <v>-78.31571438999993</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>776.4463760899999</v>
+        <v>867.8737722249999</v>
       </c>
       <c r="Z4" t="n">
-        <v>698.1306617</v>
+        <v>886.1217859999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>-78.31571438999993</v>
+        <v>18.248013775</v>
       </c>
       <c r="AB4" t="n">
-        <v>22100</v>
+        <v>2.542887919710556</v>
       </c>
       <c r="AC4" t="n">
-        <v>19871</v>
+        <v>4.011443103892623</v>
       </c>
       <c r="AD4" t="n">
-        <v>-2229.000000000004</v>
+        <v>1.468555184182067</v>
       </c>
       <c r="AE4" t="n">
-        <v>3819889612.178071</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+        <v>1.148844186667105</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.148844186667105</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>2.220446049250313e-16</v>
+      </c>
       <c r="AH4" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -974,24 +968,24 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>invested, remaining_commitment, distributions, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DriveNets</t>
+          <t>MGX I Denali Holding LP</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1006,95 +1000,95 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Partially Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Partially Realized</t>
+          <t>Unrealized</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="K5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>300</v>
+        <v>27.67275042834596</v>
       </c>
       <c r="N5" t="n">
-        <v>300</v>
+        <v>35.652964</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>7.980213571654037</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>7.980213571654037</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-7.980213571654037</v>
       </c>
       <c r="S5" t="n">
-        <v>84.80448613999999</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>84.80448613999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>506.5024466568</v>
+        <v>62.794035</v>
       </c>
       <c r="W5" t="n">
-        <v>497.5350567066</v>
+        <v>62.794035</v>
       </c>
       <c r="X5" t="n">
-        <v>-8.967389950199959</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>291.3069327968</v>
+        <v>35.12128457165404</v>
       </c>
       <c r="Z5" t="n">
-        <v>282.3395428466</v>
+        <v>27.141071</v>
       </c>
       <c r="AA5" t="n">
-        <v>-8.967389950200015</v>
+        <v>-7.980213571654033</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.971023109322667</v>
+        <v>2.269164937637653</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.941131809488667</v>
+        <v>1.761257072483511</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.02989129983400041</v>
+        <v>-0.507907865154142</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.1821719849102789</v>
+        <v>0.7757347398913037</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1745459048509513</v>
+        <v>0.7757347398913037</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.007626080059327578</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1103,24 +1097,24 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>carrying_value, gain</t>
+          <t>invested, remaining_commitment, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MGX 1 Strategic Co-invest</t>
+          <t>MGX I LP</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1154,77 +1148,73 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>296.60196</v>
+        <v>1524.145076</v>
       </c>
       <c r="K6" t="n">
-        <v>296.60196</v>
+        <v>1524.145076</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>562.4995575749999</v>
+        <v>437.0838774046402</v>
       </c>
       <c r="N6" t="n">
-        <v>562.499557575</v>
+        <v>350.846909</v>
       </c>
       <c r="O6" t="n">
-        <v>1.13686837721616e-13</v>
+        <v>-86.23696840464021</v>
       </c>
       <c r="P6" t="n">
-        <v>-265.8975975749999</v>
+        <v>1087.06119859536</v>
       </c>
       <c r="Q6" t="n">
-        <v>-265.897597575</v>
+        <v>1173.298167</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.13686837721616e-13</v>
+        <v>86.23696840463981</v>
       </c>
       <c r="S6" t="n">
-        <v>249.9999988</v>
+        <v>91.05395026651516</v>
       </c>
       <c r="T6" t="n">
-        <v>249.9999988</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>2.842170943040401e-14</v>
+        <v>-91.05395026651516</v>
       </c>
       <c r="V6" t="n">
-        <v>741.8567860000001</v>
+        <v>948.484252</v>
       </c>
       <c r="W6" t="n">
-        <v>1180.373331</v>
+        <v>948.484252</v>
       </c>
       <c r="X6" t="n">
-        <v>438.516545</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>429.3572272250001</v>
+        <v>602.454324861875</v>
       </c>
       <c r="Z6" t="n">
-        <v>867.8737722249999</v>
+        <v>597.637343</v>
       </c>
       <c r="AA6" t="n">
-        <v>438.5165449999998</v>
+        <v>-4.816981861874979</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.763302337651621</v>
+        <v>2.378349456491481</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.542887919710556</v>
+        <v>2.703413448057483</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.779585582058935</v>
+        <v>0.3250639915660019</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.6452389979024198</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.148844186667105</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0.5036051887646855</v>
-      </c>
+        <v>1.608035438909162</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -1232,24 +1222,24 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>invested, remaining_commitment, distributions, gain, tvpi, irr</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MGX I Denali Holding LP</t>
+          <t>New Space Capital Fund I</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1274,82 +1264,86 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>35.652964</v>
+        <v>26.7196311505</v>
       </c>
       <c r="K7" t="n">
-        <v>35.652964</v>
+        <v>26.7823643474</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.06273319689999823</v>
       </c>
       <c r="M7" t="n">
-        <v>27.67275042834596</v>
+        <v>17.80166535</v>
       </c>
       <c r="N7" t="n">
-        <v>27.67275042834596</v>
+        <v>16.87804819658807</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.9236171534119322</v>
       </c>
       <c r="P7" t="n">
-        <v>7.980213571654037</v>
+        <v>8.917965800499999</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.980213571654037</v>
+        <v>9.904316150811932</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.9863503503119322</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>6.50828684</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>6.7779339379808</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.2696470979807994</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>54.1676251908</v>
       </c>
       <c r="W7" t="n">
-        <v>62.794035</v>
+        <v>57.15618120708599</v>
       </c>
       <c r="X7" t="n">
-        <v>62.794035</v>
+        <v>2.988556016285983</v>
       </c>
       <c r="Y7" t="n">
-        <v>-27.67275042834596</v>
+        <v>42.87424668079999</v>
       </c>
       <c r="Z7" t="n">
-        <v>35.12128457165404</v>
+        <v>47.05606694847872</v>
       </c>
       <c r="AA7" t="n">
-        <v>62.79403500000001</v>
+        <v>4.181820267678724</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.408440212634375</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.269164937637653</v>
+        <v>3.788004063052219</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.269164937637653</v>
-      </c>
-      <c r="AE7" t="inlineStr"/>
+        <v>0.3795638504178442</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1994548830844582</v>
+      </c>
       <c r="AF7" t="n">
-        <v>0.7757347398913037</v>
-      </c>
-      <c r="AG7" t="inlineStr"/>
+        <v>0.1994548830844582</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.775557561562891e-17</v>
+      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -1357,24 +1351,24 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>committed, invested, remaining_commitment, distributions, carrying_value, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MGX I LP</t>
+          <t>New Space Capital GP Com SCSp</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1399,85 +1393,85 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>GX Investments Ltd : MGX and Related Investments</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1524.145076</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="K8" t="n">
-        <v>1524.145076</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>437.0838774046402</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="N8" t="n">
-        <v>437.0838774046402</v>
+        <v>2.705882352941176</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1087.06119859536</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1087.06119859536</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.273736754432321e-13</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>91.05395026651516</v>
+        <v>0.20616173</v>
       </c>
       <c r="T8" t="n">
-        <v>91.05395026651516</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.20616173</v>
       </c>
       <c r="V8" t="n">
-        <v>644.14725737</v>
+        <v>3.858379496274193</v>
       </c>
       <c r="W8" t="n">
-        <v>948.484252</v>
+        <v>6.786449200178311</v>
       </c>
       <c r="X8" t="n">
-        <v>304.3369946299999</v>
+        <v>2.928069703904118</v>
       </c>
       <c r="Y8" t="n">
-        <v>298.117330231875</v>
+        <v>1.358658873333016</v>
       </c>
       <c r="Z8" t="n">
-        <v>602.454324861875</v>
+        <v>4.080566847237135</v>
       </c>
       <c r="AA8" t="n">
-        <v>304.33699463</v>
+        <v>2.721907973904119</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.682059773062474</v>
+        <v>1.502113061883941</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.378349456491481</v>
+        <v>2.508035573978941</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.6962896834290071</v>
+        <v>1.005922512095</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.8586539373442278</v>
+        <v>0.1156541964277766</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.608035438909162</v>
+        <v>0.1156541964277766</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.7493815015649344</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1486,24 +1480,24 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>distributions, carrying_value, gain, tvpi</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Space Capital Fund I</t>
+          <t>North Summit Capital Fund</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1537,76 +1531,76 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>26.7196311505</v>
+        <v>83.361611</v>
       </c>
       <c r="K9" t="n">
-        <v>26.7196311505</v>
+        <v>83.361611</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>17.80166535</v>
+        <v>83.361611</v>
       </c>
       <c r="N9" t="n">
-        <v>17.80166535</v>
+        <v>83.361611</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>8.917965800499999</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>8.917965800499999</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>6.50828684</v>
+        <v>7.875571</v>
       </c>
       <c r="T9" t="n">
-        <v>6.50828684</v>
+        <v>7.875571</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>26.095994627985</v>
+        <v>69.98505299999999</v>
       </c>
       <c r="W9" t="n">
-        <v>54.1676251908</v>
+        <v>72.566225</v>
       </c>
       <c r="X9" t="n">
-        <v>28.071630562815</v>
+        <v>2.581172000000009</v>
       </c>
       <c r="Y9" t="n">
-        <v>14.802616117985</v>
+        <v>-5.500987000000009</v>
       </c>
       <c r="Z9" t="n">
-        <v>42.87424668079999</v>
+        <v>-2.919815</v>
       </c>
       <c r="AA9" t="n">
-        <v>28.07163056281499</v>
+        <v>2.581172000000009</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.831529849985917</v>
+        <v>0.9340105483326131</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.408440212634375</v>
+        <v>0.9649741054068641</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.576910362648458</v>
+        <v>0.03096355707425102</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.07373103259662646</v>
+        <v>-0.01242878543472056</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.1994548830844582</v>
+        <v>-0.01242878543472056</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.1257238504878317</v>
+        <v>1.734723475976807e-18</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1615,24 +1609,24 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi, irr</t>
+          <t>carrying_value, gain</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New Space Capital GP Com SCSp</t>
+          <t>ONT plc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1657,28 +1651,28 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>G42 Investments AI Holding RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="K10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="N10" t="n">
-        <v>2.705882352941176</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1693,49 +1687,49 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>3.655776071404095</v>
+        <v>67.52236550879999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.858379496274193</v>
+        <v>105.22733244336</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2026034248700976</v>
+        <v>37.70496693456001</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.156055448462918</v>
+        <v>-73.94789416556648</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.358658873333016</v>
+        <v>-36.2429272310065</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.2026034248700983</v>
+        <v>37.70496693455998</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.4272378831276</v>
+        <v>0.4772901786157859</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.502113061883941</v>
+        <v>0.743812393400353</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.07487517875634087</v>
+        <v>0.2665222147845671</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.1074641933261324</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1156541964277766</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.008190003101644208</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -1751,66 +1745,66 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ONT plc</t>
+          <t>Sinovation Disrupt Fund, L.P.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unrealized</t>
+          <t>Realized</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>G42 Investments AI Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>141.4702596743665</v>
+        <v>41.967904</v>
       </c>
       <c r="K11" t="n">
-        <v>141.4702596743665</v>
+        <v>50</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>8.032096000000003</v>
       </c>
       <c r="M11" t="n">
-        <v>141.4702596743665</v>
+        <v>41.967904</v>
       </c>
       <c r="N11" t="n">
-        <v>141.4702596743665</v>
+        <v>24.959693</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.842170943040401e-14</v>
+        <v>-17.008211</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -1822,49 +1816,49 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>42.41173234999999</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>25.40352135</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-17.00821099999999</v>
       </c>
       <c r="V11" t="n">
-        <v>72.94484711592</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>67.52236550879999</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.422481607120005</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>-68.5254125584465</v>
+        <v>0.4438283499999969</v>
       </c>
       <c r="Z11" t="n">
-        <v>-73.94789416556648</v>
+        <v>0.4438283500000004</v>
       </c>
       <c r="AA11" t="n">
-        <v>-5.422481607119977</v>
+        <v>3.552713678800501e-15</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.5156196594522625</v>
+        <v>1.010575423304438</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4772901786157859</v>
+        <v>1.017781803245737</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.03832948083647658</v>
+        <v>0.007206379941299135</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.1036411286787608</v>
+        <v>0.007642245213040634</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.1135171173653592</v>
+        <v>0.007642245213040634</v>
       </c>
       <c r="AG11" t="n">
-        <v>-0.009875988686598405</v>
+        <v>-8.673617379884035e-19</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -1873,34 +1867,34 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>carrying_value, gain</t>
+          <t>committed, invested, distributions</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Verses AI Inc</t>
+          <t>WLD Tokens</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Live</t>
+          <t>Exited</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1915,28 +1909,28 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>G42 Capital SPV RSC Ltd</t>
+          <t>MOZN Holding RSC Ltd</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="K12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>0.006875</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1951,46 +1945,46 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.1338020955555556</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1338020955555556</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>-9.866197904444444</v>
+        <v>99.99312500000001</v>
       </c>
       <c r="Z12" t="n">
-        <v>-10</v>
+        <v>99.99312500000001</v>
       </c>
       <c r="AA12" t="n">
-        <v>-0.1338020955555557</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.01338020955555556</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>-0.01338020955555556</v>
-      </c>
+        <v>14545.45454545455</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="n">
-        <v>-0.8809058327281951</v>
-      </c>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+        <v>727.8222082232667</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>727.8222082232667</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
       <c r="AH12" t="inlineStr">
         <is>
           <t>Changed</t>
@@ -1998,19 +1992,19 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>carrying_value, gain, irr</t>
+          <t>tvpi</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2085,40 +2079,40 @@
         <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.776086049999998</v>
+        <v>8.399903950000001</v>
       </c>
       <c r="W13" t="n">
-        <v>8.399903950000001</v>
+        <v>8.309024000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.376182099999998</v>
+        <v>-0.09087994999999971</v>
       </c>
       <c r="Y13" t="n">
-        <v>-14.75516395</v>
+        <v>-16.13134605</v>
       </c>
       <c r="Z13" t="n">
-        <v>-16.13134605</v>
+        <v>-16.222226</v>
       </c>
       <c r="AA13" t="n">
-        <v>-1.376182099999998</v>
+        <v>-0.09087994999999793</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.3985156096815286</v>
+        <v>0.3424164667515924</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3424164667515924</v>
+        <v>0.3387118063694268</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.05609914292993623</v>
+        <v>-0.003704660382165603</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0.2201095569344076</v>
+        <v>-0.246693162941984</v>
       </c>
       <c r="AF13" t="n">
         <v>-0.246693162941984</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.02658360600757637</v>
+        <v>5.551115123125783e-17</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2127,7 +2121,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>carrying_value, gain, tvpi</t>
+          <t>carrying_value, gain</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2245,12 +2239,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2326,12 +2320,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2370,25 +2364,25 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>41.967904</v>
+        <v>50</v>
       </c>
       <c r="K3" t="n">
-        <v>41.967904</v>
+        <v>24.959693</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>42.41173234999999</v>
+        <v>25.40352135</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4438283499999969</v>
+        <v>0.4438283500000004</v>
       </c>
       <c r="P3" t="n">
-        <v>1.010575423304438</v>
+        <v>1.017781803245737</v>
       </c>
       <c r="Q3" t="n">
         <v>0.007642245213040634</v>
@@ -2407,12 +2401,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2488,12 +2482,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2569,12 +2563,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2648,12 +2642,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2701,13 +2695,13 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>7.942192529999998</v>
+        <v>7.942192529999999</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.918472331522564</v>
+        <v>2.918472331522565</v>
       </c>
       <c r="P7" t="n">
         <v>1.580938471136805</v>
@@ -2729,12 +2723,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2808,12 +2802,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2889,12 +2883,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2968,12 +2962,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3047,12 +3041,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3108,9 +3102,7 @@
       <c r="O12" t="n">
         <v>99.99312500000001</v>
       </c>
-      <c r="P12" t="n">
-        <v>14545.45454545455</v>
-      </c>
+      <c r="P12" t="inlineStr"/>
       <c r="Q12" t="n">
         <v>727.8222082232667</v>
       </c>
@@ -3128,12 +3120,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -3209,12 +3201,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -3290,12 +3282,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -3346,14 +3338,12 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>698.16579661</v>
+        <v>647.32558184</v>
       </c>
       <c r="O15" t="n">
-        <v>698.1306617</v>
-      </c>
-      <c r="P15" t="n">
-        <v>19871</v>
-      </c>
+        <v>647.29044693</v>
+      </c>
+      <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
@@ -3369,12 +3359,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -3450,12 +3440,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3531,12 +3521,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -3575,13 +3565,13 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>60.81986291</v>
+        <v>60.81986292</v>
       </c>
       <c r="K18" t="n">
         <v>60.81986292</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.000000082740371e-08</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
         <v>0</v>
@@ -3612,12 +3602,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3693,12 +3683,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -3772,12 +3762,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -3819,10 +3809,10 @@
         <v>17.1125</v>
       </c>
       <c r="K21" t="n">
-        <v>15.7263875</v>
+        <v>15.726388</v>
       </c>
       <c r="L21" t="n">
-        <v>1.386112500000001</v>
+        <v>1.386113</v>
       </c>
       <c r="M21" t="n">
         <v>0</v>
@@ -3831,10 +3821,10 @@
         <v>14.034903</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6914845</v>
+        <v>-1.691485</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8924429084556132</v>
+        <v>0.8924428800815546</v>
       </c>
       <c r="Q21" t="n">
         <v>-0.02935277732578557</v>
@@ -3853,12 +3843,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -3912,10 +3902,10 @@
         <v>497.5350567066</v>
       </c>
       <c r="O22" t="n">
-        <v>282.3395428466</v>
+        <v>282.3395428465999</v>
       </c>
       <c r="P22" t="n">
-        <v>1.941131809488667</v>
+        <v>1.941131809488666</v>
       </c>
       <c r="Q22" t="n">
         <v>0.1745459048509513</v>
@@ -3934,12 +3924,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3978,25 +3968,25 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>26.7196311505</v>
+        <v>26.7823643474</v>
       </c>
       <c r="K23" t="n">
-        <v>17.80166535</v>
+        <v>16.87804819658807</v>
       </c>
       <c r="L23" t="n">
-        <v>8.917965800499999</v>
+        <v>9.904316150811932</v>
       </c>
       <c r="M23" t="n">
-        <v>6.50828684</v>
+        <v>6.7779339379808</v>
       </c>
       <c r="N23" t="n">
-        <v>54.1676251908</v>
+        <v>57.15618120708599</v>
       </c>
       <c r="O23" t="n">
-        <v>42.87424668079999</v>
+        <v>47.05606694847872</v>
       </c>
       <c r="P23" t="n">
-        <v>3.408440212634375</v>
+        <v>3.788004063052219</v>
       </c>
       <c r="Q23" t="n">
         <v>0.1994548830844582</v>
@@ -4015,12 +4005,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -4068,16 +4058,16 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.20616173</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.858379496274193</v>
+        <v>6.786449200178311</v>
       </c>
       <c r="O24" t="n">
-        <v>1.358658873333016</v>
+        <v>4.080566847237135</v>
       </c>
       <c r="P24" t="n">
-        <v>1.502113061883941</v>
+        <v>2.508035573978941</v>
       </c>
       <c r="Q24" t="n">
         <v>0.1156541964277766</v>
@@ -4096,12 +4086,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -4152,13 +4142,13 @@
         <v>7.875571</v>
       </c>
       <c r="N25" t="n">
-        <v>69.98505299999999</v>
+        <v>72.566225</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.500987000000009</v>
+        <v>-2.919815</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9340105483326131</v>
+        <v>0.9649741054068641</v>
       </c>
       <c r="Q25" t="n">
         <v>-0.01242878543472056</v>
@@ -4177,12 +4167,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -4233,13 +4223,13 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>8.399903950000001</v>
+        <v>8.309024000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-16.13134605</v>
+        <v>-16.222226</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3424164667515924</v>
+        <v>0.3387118063694268</v>
       </c>
       <c r="Q26" t="n">
         <v>-0.246693162941984</v>
@@ -4258,12 +4248,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -4305,22 +4295,22 @@
         <v>296.60196</v>
       </c>
       <c r="K27" t="n">
-        <v>562.499557575</v>
+        <v>294.251545</v>
       </c>
       <c r="L27" t="n">
-        <v>-265.897597575</v>
+        <v>2.350415</v>
       </c>
       <c r="M27" t="n">
-        <v>249.9999988</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>1180.373331</v>
       </c>
       <c r="O27" t="n">
-        <v>867.8737722249999</v>
+        <v>886.1217859999999</v>
       </c>
       <c r="P27" t="n">
-        <v>2.542887919710556</v>
+        <v>4.011443103892623</v>
       </c>
       <c r="Q27" t="n">
         <v>1.148844186667105</v>
@@ -4339,12 +4329,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -4420,12 +4410,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -4467,10 +4457,10 @@
         <v>35.652964</v>
       </c>
       <c r="K29" t="n">
-        <v>27.67275042834596</v>
+        <v>35.652964</v>
       </c>
       <c r="L29" t="n">
-        <v>7.980213571654037</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -4479,10 +4469,10 @@
         <v>62.794035</v>
       </c>
       <c r="O29" t="n">
-        <v>35.12128457165404</v>
+        <v>27.141071</v>
       </c>
       <c r="P29" t="n">
-        <v>2.269164937637653</v>
+        <v>1.761257072483511</v>
       </c>
       <c r="Q29" t="n">
         <v>0.7757347398913037</v>
@@ -4501,12 +4491,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -4548,46 +4538,36 @@
         <v>1524.145076</v>
       </c>
       <c r="K30" t="n">
-        <v>437.0838774046402</v>
+        <v>350.846909</v>
       </c>
       <c r="L30" t="n">
-        <v>1087.06119859536</v>
+        <v>1173.298167</v>
       </c>
       <c r="M30" t="n">
-        <v>91.05395026651516</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
         <v>948.484252</v>
       </c>
       <c r="O30" t="n">
-        <v>602.454324861875</v>
+        <v>597.637343</v>
       </c>
       <c r="P30" t="n">
-        <v>2.378349456491481</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.608035438909162</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>Q2'26 capital account statement</t>
-        </is>
-      </c>
+        <v>2.703413448057483</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -4597,12 +4577,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Applied AI Corporation Limited</t>
+          <t>MGX I LP + Denali</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4612,63 +4592,49 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mozn</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+          <t>G42 Holding</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>2024</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A Prefs</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>1559.79804</v>
       </c>
       <c r="K31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1559.79804</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>38.46473015</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>23.46473015</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.564315343333333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.379698656873341</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Marked up, being held at 2.27X as per the last round</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -4683,7 +4649,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beyond Limits</t>
+          <t>Applied AI Corporation Limited</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4698,19 +4664,19 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>A Prefs</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -4719,16 +4685,16 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>21.7</v>
+        <v>38.46473015</v>
       </c>
       <c r="O32" t="n">
-        <v>-68.3</v>
+        <v>23.46473015</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2411111111111111</v>
+        <v>2.564315343333333</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.2038134167490631</v>
+        <v>0.379698656873341</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -4737,19 +4703,19 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
+          <t>Marked up, being held at 2.27X as per the last round</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -4764,7 +4730,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (1)</t>
+          <t>Beyond Limits</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4779,37 +4745,37 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Class A/B</t>
+          <t>C Prefs</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>39.99998336</v>
+        <v>90</v>
       </c>
       <c r="K33" t="n">
-        <v>39.99998335999999</v>
+        <v>90</v>
       </c>
       <c r="L33" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>286.4823928099999</v>
+        <v>21.7</v>
       </c>
       <c r="O33" t="n">
-        <v>246.4824094499999</v>
+        <v>-68.3</v>
       </c>
       <c r="P33" t="n">
-        <v>7.162062799668123</v>
+        <v>0.2411111111111111</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5091940466191891</v>
+        <v>-0.2038134167490631</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -4818,19 +4784,19 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Marked to the latest round</t>
+          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4845,7 +4811,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E-line Ventures LLC</t>
+          <t>Cerebras Systems Inc (1)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4860,19 +4826,19 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B Prefs</t>
+          <t>Class A/B</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -4881,16 +4847,16 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>7.1</v>
+        <v>265.62083464</v>
       </c>
       <c r="O34" t="n">
-        <v>1.1</v>
+        <v>225.62085128</v>
       </c>
       <c r="P34" t="n">
-        <v>1.183333333333333</v>
+        <v>6.640523628457831</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.059274505967036</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
@@ -4899,19 +4865,19 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Marked to the latest round</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4926,7 +4892,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Endless Studios LLC</t>
+          <t>E-line Ventures LLC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4941,19 +4907,19 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A Pref Units</t>
+          <t>B Prefs</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -4962,16 +4928,16 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.5</v>
+        <v>1.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8125</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.05616841430472284</v>
+        <v>0.059274505967036</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -4987,12 +4953,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5007,7 +4973,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flyr Inc</t>
+          <t>Endless Studios LLC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -5022,19 +4988,19 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B-1,2 Prefs</t>
+          <t>A Pref Units</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -5043,16 +5009,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>14.6</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
-        <v>4.6</v>
+        <v>-1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.46</v>
+        <v>0.8125</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.05695277639397291</v>
+        <v>-0.05616841430472284</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -5061,19 +5027,19 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>As per the recent fund raise for Series D</t>
+          <t>Ardent Valuation as of 31 Dec 25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5088,7 +5054,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heygears</t>
+          <t>Flyr Inc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5103,19 +5069,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Registered Capital</t>
+          <t>B-1,2 Prefs</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -5124,16 +5090,16 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>71.91884647972564</v>
+        <v>14.6</v>
       </c>
       <c r="O37" t="n">
-        <v>11.91884647972564</v>
+        <v>4.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.198647441328761</v>
+        <v>1.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03249740083723869</v>
+        <v>0.05695277639397291</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -5142,19 +5108,19 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
+          <t>As per the recent fund raise for Series D</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5169,7 +5135,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ONT plc</t>
+          <t>Heygears</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5189,14 +5155,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Ordinary Shares</t>
+          <t>Registered Capital</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -5205,16 +5171,16 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>67.52236550879999</v>
+        <v>71.91884647972564</v>
       </c>
       <c r="O38" t="n">
-        <v>-73.94789416556648</v>
+        <v>11.91884647972564</v>
       </c>
       <c r="P38" t="n">
-        <v>0.4772901786157859</v>
+        <v>1.198647441328761</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.1135171173653592</v>
+        <v>0.03249740083723869</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -5223,19 +5189,19 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Listed &amp; marked to market</t>
+          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5250,7 +5216,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tools for Humanity Corporation</t>
+          <t>ONT plc</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5265,19 +5231,19 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>Ordinary Shares</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="K39" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -5286,16 +5252,16 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.2</v>
+        <v>105.22733244336</v>
       </c>
       <c r="O39" t="n">
-        <v>-13.79999894</v>
+        <v>-36.2429272310065</v>
       </c>
       <c r="P39" t="n">
-        <v>0.08000000565333373</v>
+        <v>0.743812393400353</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.5486080580793249</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -5304,19 +5270,19 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Listed &amp; marked to market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5331,59 +5297,140 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Tools for Humanity Corporation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C Prefs</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="K40" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-13.79999894</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.08000000565333373</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.5486080580793249</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>eSpace</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>B Prefs</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>15</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>15</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>230.00750916</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O41" t="n">
         <v>215.00750916</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P41" t="n">
         <v>15.333833944</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="Q41" t="n">
         <v>1.101240687453752</v>
       </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t xml:space="preserve">Marked up, as converted as per the latest priced round </t>
         </is>
@@ -5400,7 +5447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S40"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5503,12 +5550,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -5570,7 +5617,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -5582,12 +5629,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -5645,11 +5692,11 @@
         <v>1.010575423304438</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.007642245213040372</v>
+        <v>0.007642245213040634</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -5661,12 +5708,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -5728,7 +5775,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -5740,12 +5787,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -5807,7 +5854,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5819,12 +5866,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -5884,7 +5931,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5896,12 +5943,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -5963,7 +6010,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5975,12 +6022,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6040,7 +6087,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -6052,12 +6099,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -6119,7 +6166,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -6131,12 +6178,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -6196,7 +6243,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -6208,12 +6255,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -6273,7 +6320,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -6285,12 +6332,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -6352,7 +6399,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -6364,12 +6411,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -6431,7 +6478,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6443,12 +6490,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -6506,11 +6553,11 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.307883035229347e-17</v>
+        <v>-2.543922105633999e-17</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -6522,12 +6569,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -6576,20 +6623,18 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>776.481511</v>
+        <v>698.16579661</v>
       </c>
       <c r="O15" t="n">
-        <v>776.4463760899999</v>
+        <v>698.1306617</v>
       </c>
       <c r="P15" t="n">
-        <v>22100</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3819889612.178071</v>
-      </c>
+        <v>19871</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6601,12 +6646,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -6664,11 +6709,11 @@
         <v>1.00499965</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.003094171778386556</v>
+        <v>0.002940024332733333</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -6680,12 +6725,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -6743,11 +6788,11 @@
         <v>1.0236848428675</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01176105659818794</v>
+        <v>0.01127988670501709</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -6759,12 +6804,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -6822,11 +6867,11 @@
         <v>1.095023575400061</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.140820597957165</v>
+        <v>0.1246650272180429</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -6838,12 +6883,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -6901,11 +6946,11 @@
         <v>1.00000001</v>
       </c>
       <c r="Q19" t="n">
-        <v>9.335038486138602e-09</v>
+        <v>8.649289246403672e-09</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -6917,12 +6962,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -6971,20 +7016,18 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1338020955555556</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-9.866197904444444</v>
+        <v>-10</v>
       </c>
       <c r="P20" t="n">
-        <v>0.01338020955555556</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-0.8809058327281951</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -6996,12 +7039,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -7050,16 +7093,16 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>12.683716</v>
+        <v>14.034903</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.042671499999999</v>
+        <v>-1.6914845</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8065244481607744</v>
+        <v>0.8924429084556132</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.05492458454080403</v>
+        <v>-0.02935277732578557</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -7068,19 +7111,19 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>Q1'26  capital account statement</t>
+          <t>Q2'26 capital account statement</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -7129,20 +7172,20 @@
         <v>84.80448613999999</v>
       </c>
       <c r="N22" t="n">
-        <v>506.5024466568</v>
+        <v>497.5350567066</v>
       </c>
       <c r="O22" t="n">
-        <v>291.3069327968</v>
+        <v>282.3395428466</v>
       </c>
       <c r="P22" t="n">
-        <v>1.971023109322667</v>
+        <v>1.941131809488667</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1821719849102789</v>
+        <v>0.1745459048509513</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -7154,12 +7197,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -7208,16 +7251,16 @@
         <v>6.50828684</v>
       </c>
       <c r="N23" t="n">
-        <v>26.095994627985</v>
+        <v>54.1676251908</v>
       </c>
       <c r="O23" t="n">
-        <v>14.802616117985</v>
+        <v>42.87424668079999</v>
       </c>
       <c r="P23" t="n">
-        <v>1.831529849985917</v>
+        <v>3.408440212634375</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.07373103259662646</v>
+        <v>0.1994548830844582</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -7226,19 +7269,19 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Q1'26  capital account statement</t>
+          <t>Q2'26 Limited Partner Statement (NewSpace Capital Fund S.C.S., for G42 Investments AI Holding Limited)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -7287,20 +7330,20 @@
         <v>0.20616173</v>
       </c>
       <c r="N24" t="n">
-        <v>3.655776071404095</v>
+        <v>3.858379496274193</v>
       </c>
       <c r="O24" t="n">
-        <v>1.156055448462918</v>
+        <v>1.358658873333016</v>
       </c>
       <c r="P24" t="n">
-        <v>1.4272378831276</v>
+        <v>1.502113061883941</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1074641933261324</v>
+        <v>0.1156541964277766</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -7312,12 +7355,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -7375,11 +7418,11 @@
         <v>0.9340105483326131</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.01260462699509538</v>
+        <v>-0.01242878543472056</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -7391,12 +7434,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -7445,20 +7488,20 @@
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>9.776086049999998</v>
+        <v>8.399903950000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-14.75516395</v>
+        <v>-16.13134605</v>
       </c>
       <c r="P26" t="n">
-        <v>0.3985156096815286</v>
+        <v>0.3424164667515924</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.2201095569344076</v>
+        <v>-0.246693162941984</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -7470,12 +7513,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -7515,25 +7558,25 @@
         <v>296.60196</v>
       </c>
       <c r="K27" t="n">
-        <v>562.4995575749999</v>
+        <v>562.499557575</v>
       </c>
       <c r="L27" t="n">
-        <v>-265.8975975749999</v>
+        <v>-265.897597575</v>
       </c>
       <c r="M27" t="n">
         <v>249.9999988</v>
       </c>
       <c r="N27" t="n">
-        <v>741.8567860000001</v>
+        <v>1180.373331</v>
       </c>
       <c r="O27" t="n">
-        <v>429.3572272250001</v>
+        <v>867.8737722249999</v>
       </c>
       <c r="P27" t="n">
-        <v>1.763302337651621</v>
+        <v>2.542887919710556</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6452389979024198</v>
+        <v>1.148844186667105</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -7542,19 +7585,19 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Q4'25  capital account statement</t>
+          <t>Q2'26 capital account statement</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -7612,11 +7655,11 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>-3.349775818301575e-18</v>
+        <v>-3.037872421094163e-17</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -7628,12 +7671,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -7682,27 +7725,37 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>62.794035</v>
       </c>
       <c r="O29" t="n">
-        <v>-27.67275042834596</v>
+        <v>35.12128457165404</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+        <v>2.269164937637653</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.7757347398913037</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>Q2'26 capital account statement</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -7751,16 +7804,16 @@
         <v>91.05395026651516</v>
       </c>
       <c r="N30" t="n">
-        <v>644.14725737</v>
+        <v>948.484252</v>
       </c>
       <c r="O30" t="n">
-        <v>298.117330231875</v>
+        <v>602.454324861875</v>
       </c>
       <c r="P30" t="n">
-        <v>1.682059773062474</v>
+        <v>2.378349456491481</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8586539373442278</v>
+        <v>1.608035438909162</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -7769,19 +7822,19 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Q4'25  capital account statement</t>
+          <t>Q2'26 capital account statement</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -7791,12 +7844,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MOZN Holding RSC Ltd</t>
+          <t>GX Investments Ltd : MGX and Related Investments</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Applied AI Corporation Limited</t>
+          <t>MGX I LP + Denali</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -7806,61 +7859,49 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Mozn</t>
+          <t>G42 Holding</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>A Prefs</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="J31" t="n">
-        <v>15</v>
+        <v>1559.79804</v>
       </c>
       <c r="K31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1559.79804</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>38.46473015</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>23.46473015</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.564315343333333</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0.3926062988552793</v>
-      </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>Marked up, being held at 2.27X as per the last round</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -7875,7 +7916,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Beyond Limits</t>
+          <t>Applied AI Corporation Limited</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -7889,18 +7930,18 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>A Prefs</t>
         </is>
       </c>
       <c r="J32" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="K32" t="n">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -7909,37 +7950,37 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>21.7</v>
+        <v>38.46473015</v>
       </c>
       <c r="O32" t="n">
-        <v>-68.3</v>
+        <v>23.46473015</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2411111111111111</v>
+        <v>2.564315343333333</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.2063146412639268</v>
+        <v>0.379698656873341</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
+          <t>Marked up, being held at 2.27X as per the last round</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -7954,7 +7995,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cerebras Systems Inc (1)</t>
+          <t>Beyond Limits</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -7968,57 +8009,57 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Class A/B</t>
+          <t>C Prefs</t>
         </is>
       </c>
       <c r="J33" t="n">
-        <v>39.99998336</v>
+        <v>90</v>
       </c>
       <c r="K33" t="n">
-        <v>39.99998335999999</v>
+        <v>90</v>
       </c>
       <c r="L33" t="n">
-        <v>7.105427357601002e-15</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>318.618131</v>
+        <v>21.7</v>
       </c>
       <c r="O33" t="n">
-        <v>278.61814764</v>
+        <v>-68.3</v>
       </c>
       <c r="P33" t="n">
-        <v>7.965456588629942</v>
+        <v>0.2411111111111111</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5552594721409149</v>
+        <v>-0.2038134167490631</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Marked to the latest round</t>
+          <t>Ardent Dec'25 | 50% haircut recent convertible price during Q4'25</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -8033,7 +8074,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>E-line Ventures LLC</t>
+          <t>Cerebras Systems Inc (1)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -8047,57 +8088,57 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>B Prefs</t>
+          <t>Class A/B</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>6</v>
+        <v>39.99998336</v>
       </c>
       <c r="K34" t="n">
-        <v>6</v>
+        <v>39.99998335999999</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>7.105427357601002e-15</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>7.1</v>
+        <v>286.4823928099999</v>
       </c>
       <c r="O34" t="n">
-        <v>1.1</v>
+        <v>246.4824094499999</v>
       </c>
       <c r="P34" t="n">
-        <v>1.183333333333333</v>
+        <v>7.162062799668123</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.06110129482885591</v>
+        <v>0.5091940466191891</v>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Marked to the latest round</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -8112,7 +8153,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Endless Studios LLC</t>
+          <t>E-line Ventures LLC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -8126,18 +8167,18 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>A Pref Units</t>
+          <t>B Prefs</t>
         </is>
       </c>
       <c r="J35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -8146,20 +8187,20 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.5</v>
+        <v>1.1</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8125</v>
+        <v>1.183333333333333</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.05749759530151016</v>
+        <v>0.059274505967036</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -8171,12 +8212,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -8191,7 +8232,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Flyr Inc</t>
+          <t>Endless Studios LLC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -8205,18 +8246,18 @@
         </is>
       </c>
       <c r="H36" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>B-1,2 Prefs</t>
+          <t>A Pref Units</t>
         </is>
       </c>
       <c r="J36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -8225,37 +8266,37 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>14.6</v>
+        <v>6.5</v>
       </c>
       <c r="O36" t="n">
-        <v>4.6</v>
+        <v>-1.5</v>
       </c>
       <c r="P36" t="n">
-        <v>1.46</v>
+        <v>0.8125</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.05768928132215393</v>
+        <v>-0.05616841430472284</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>As per the recent fund raise for Series D</t>
+          <t>Ardent Valuation as of 31 Dec 25</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -8270,7 +8311,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Heygears</t>
+          <t>Flyr Inc</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -8284,18 +8325,18 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Registered Capital</t>
+          <t>B-1,2 Prefs</t>
         </is>
       </c>
       <c r="J37" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -8304,37 +8345,37 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>71.91884647972564</v>
+        <v>14.6</v>
       </c>
       <c r="O37" t="n">
-        <v>11.91884647972564</v>
+        <v>4.6</v>
       </c>
       <c r="P37" t="n">
-        <v>1.198647441328761</v>
+        <v>1.46</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03300003378924135</v>
+        <v>0.05695277639397291</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
+          <t>As per the recent fund raise for Series D</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -8349,7 +8390,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ONT plc</t>
+          <t>Heygears</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -8367,14 +8408,14 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Ordinary Shares</t>
+          <t>Registered Capital</t>
         </is>
       </c>
       <c r="J38" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="K38" t="n">
-        <v>141.4702596743665</v>
+        <v>60</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -8383,37 +8424,37 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>72.94484711592</v>
+        <v>71.91884647972564</v>
       </c>
       <c r="O38" t="n">
-        <v>-68.5254125584465</v>
+        <v>11.91884647972564</v>
       </c>
       <c r="P38" t="n">
-        <v>0.5156196594522625</v>
+        <v>1.198647441328761</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.1036411286787608</v>
+        <v>0.03249740083723869</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Listed &amp; marked to market</t>
+          <t xml:space="preserve"> Priced round at RMB 141.2 per share | Mar'26</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -8428,7 +8469,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tools for Humanity Corporation</t>
+          <t>ONT plc</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -8442,18 +8483,18 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>C Prefs</t>
+          <t>Ordinary Shares</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="K39" t="n">
-        <v>14.99999894</v>
+        <v>141.4702596743665</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -8462,37 +8503,37 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1.2</v>
+        <v>67.52236550879999</v>
       </c>
       <c r="O39" t="n">
-        <v>-13.79999894</v>
+        <v>-73.94789416556648</v>
       </c>
       <c r="P39" t="n">
-        <v>0.08000000565333373</v>
+        <v>0.4772901786157859</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.5583683841274028</v>
+        <v>-0.1135171173653592</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Ardent Valuation as of 31 Dec 25</t>
+          <t>Listed &amp; marked to market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -8507,57 +8548,136 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
+          <t>Tools for Humanity Corporation</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Unrealized</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Mozn</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>2023</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>C Prefs</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="K40" t="n">
+        <v>14.99999894</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O40" t="n">
+        <v>-13.79999894</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.08000000565333373</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>-0.5486080580793249</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Ardent Valuation as of 31 Dec 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>MOZN Holding RSC Ltd</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>eSpace</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>Unrealized</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Mozn</t>
         </is>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>2022</v>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>B Prefs</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>15</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>15</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>230.00750916</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O41" t="n">
         <v>215.00750916</v>
       </c>
-      <c r="P40" t="n">
+      <c r="P41" t="n">
         <v>15.333833944</v>
       </c>
-      <c r="Q40" t="n">
-        <v>1.138459785558989</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
+      <c r="Q41" t="n">
+        <v>1.101240687453752</v>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t xml:space="preserve">Marked up, as converted as per the latest priced round </t>
         </is>
